--- a/artfynd/A 38703-2023 artfynd.xlsx
+++ b/artfynd/A 38703-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38703-2023 artfynd.xlsx
+++ b/artfynd/A 38703-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1042,6 +1042,125 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125945819</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57824</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102623</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Trädlärka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lullula arborea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Maglehems naturreservat, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>445626</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6181097</v>
+      </c>
+      <c r="S5" t="n">
+        <v>32</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Maglehem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Petter Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Petter Olsson, Robert Rydbeck</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38703-2023 artfynd.xlsx
+++ b/artfynd/A 38703-2023 artfynd.xlsx
@@ -1047,7 +1047,7 @@
         <v>125945819</v>
       </c>
       <c r="B5" t="n">
-        <v>57824</v>
+        <v>57825</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38703-2023 artfynd.xlsx
+++ b/artfynd/A 38703-2023 artfynd.xlsx
@@ -1156,7 +1156,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Petter Olsson, Robert Rydbeck</t>
+          <t>Robert Rydbeck, Petter Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 38703-2023 artfynd.xlsx
+++ b/artfynd/A 38703-2023 artfynd.xlsx
@@ -1156,7 +1156,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Robert Rydbeck, Petter Olsson</t>
+          <t>Petter Olsson, Robert Rydbeck</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 38703-2023 artfynd.xlsx
+++ b/artfynd/A 38703-2023 artfynd.xlsx
@@ -1047,7 +1047,7 @@
         <v>125945819</v>
       </c>
       <c r="B5" t="n">
-        <v>57825</v>
+        <v>57829</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38703-2023 artfynd.xlsx
+++ b/artfynd/A 38703-2023 artfynd.xlsx
@@ -1047,7 +1047,7 @@
         <v>125945819</v>
       </c>
       <c r="B5" t="n">
-        <v>57829</v>
+        <v>57830</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Petter Olsson, Robert Rydbeck</t>
+          <t>Robert Rydbeck, Petter Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
